--- a/sourcedat.xlsx
+++ b/sourcedat.xlsx
@@ -1,8 +1,8 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookPr date1904="false" showObjects="all" backupFile="false"/>
   <workbookProtection/>
   <bookViews>
     <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="30"/>
@@ -44,7 +44,7 @@
     <sheet name="Fig.S6d" sheetId="34" state="visible" r:id="rId35"/>
     <sheet name="Fig.S6e" sheetId="35" state="visible" r:id="rId36"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <calcPr fullCalcOnLoad="true" refMode="A1" iterate="false" iterateCount="100" iterateDelta="0.0001"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
       <loext:extCalcPr stringRefSyntax="CalcA1ExcelA1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6098" uniqueCount="1737">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="6136" uniqueCount="1737">
   <si>
     <t xml:space="preserve">human_mean</t>
   </si>
@@ -5270,7 +5270,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
@@ -5305,7 +5305,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -5313,6 +5313,7 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border/>
   </borders>
   <cellStyleXfs count="20">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -5339,11 +5340,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="22" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="true"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5357,19 +5359,20 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C16"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="13.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14.69"/>
+    <col min="1" max="1" width="11.85546875" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="13.28515625" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="11.28515625" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0"/>
       <c r="B1" s="0" t="s">
         <v>0</v>
       </c>
@@ -5384,8 +5387,8 @@
       <c r="B2" s="0" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="0" t="n">
-        <v>-0.00679132106023916</v>
+      <c r="C2" s="0">
+        <v>-0.0067913210602391578</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5395,8 +5398,8 @@
       <c r="B3" s="0" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="0" t="n">
-        <v>0.075273564384272</v>
+      <c r="C3" s="0">
+        <v>0.075273564384271949</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5406,8 +5409,8 @@
       <c r="B4" s="0" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="0" t="n">
-        <v>-0.0399481182845926</v>
+      <c r="C4" s="0">
+        <v>-0.039948118284592556</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5417,8 +5420,8 @@
       <c r="B5" s="0" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="0" t="n">
-        <v>0.0894950752576578</v>
+      <c r="C5" s="0">
+        <v>0.089495075257657819</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5428,8 +5431,8 @@
       <c r="B6" s="0" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="0" t="n">
-        <v>0.0237665701365519</v>
+      <c r="C6" s="0">
+        <v>0.023766570136551871</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5439,8 +5442,8 @@
       <c r="B7" s="0" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="0" t="n">
-        <v>0.191281452085403</v>
+      <c r="C7" s="0">
+        <v>0.19128145208540332</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5450,8 +5453,8 @@
       <c r="B8" s="0" t="s">
         <v>15</v>
       </c>
-      <c r="C8" s="0" t="n">
-        <v>0.378578819296427</v>
+      <c r="C8" s="0">
+        <v>0.37857881929642745</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5461,8 +5464,8 @@
       <c r="B9" s="0" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="0" t="n">
-        <v>-0.0337053308875459</v>
+      <c r="C9" s="0">
+        <v>-0.033705330887545869</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5472,8 +5475,8 @@
       <c r="B10" s="0" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="0" t="n">
-        <v>0.0951266137723449</v>
+      <c r="C10" s="0">
+        <v>0.095126613772344895</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5483,8 +5486,8 @@
       <c r="B11" s="0" t="s">
         <v>21</v>
       </c>
-      <c r="C11" s="0" t="n">
-        <v>0.177636728000089</v>
+      <c r="C11" s="0">
+        <v>0.17763672800008928</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5494,8 +5497,8 @@
       <c r="B12" s="0" t="s">
         <v>23</v>
       </c>
-      <c r="C12" s="0" t="n">
-        <v>0.260635141450644</v>
+      <c r="C12" s="0">
+        <v>0.26063514145064409</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5505,8 +5508,8 @@
       <c r="B13" s="0" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="0" t="n">
-        <v>0.00932693626499447</v>
+      <c r="C13" s="0">
+        <v>0.0093269362649944683</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5516,8 +5519,8 @@
       <c r="B14" s="0" t="s">
         <v>27</v>
       </c>
-      <c r="C14" s="0" t="n">
-        <v>-0.0582986473797256</v>
+      <c r="C14" s="0">
+        <v>-0.05829864737972558</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5527,8 +5530,8 @@
       <c r="B15" s="0" t="s">
         <v>29</v>
       </c>
-      <c r="C15" s="0" t="n">
-        <v>0.0259825336644414</v>
+      <c r="C15" s="0">
+        <v>0.025982533664441445</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5538,15 +5541,15 @@
       <c r="B16" s="0" t="s">
         <v>31</v>
       </c>
-      <c r="C16" s="0" t="n">
-        <v>0.027849903182018</v>
+      <c r="C16" s="0">
+        <v>0.027849903182017955</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -5554,16 +5557,16 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C199"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="67.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.29"/>
+    <col min="1" max="1" width="67.14" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="11.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="16.29" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7753,10 +7756,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -7764,16 +7767,16 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C199"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="67.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.29"/>
+    <col min="1" max="1" width="67.14" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="11.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="16.29" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -9963,10 +9966,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -9974,16 +9977,16 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C199"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="67.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.29"/>
+    <col min="1" max="1" width="67.14" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="11.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="16.29" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -12173,10 +12176,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -12184,16 +12187,16 @@
 </file>
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C199"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="67.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.29"/>
+    <col min="1" max="1" width="67.14" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="11.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="16.29" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -14383,10 +14386,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -14394,16 +14397,16 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C199"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="67.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.29"/>
+    <col min="1" max="1" width="67.14" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="11.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="16.29" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -16593,10 +16596,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -16604,23 +16607,23 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L199"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="67.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="11.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="16.29"/>
+    <col min="1" max="1" width="11.71" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="11.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="8.14" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="4" max="4" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="11.71" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="16.29" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="8" max="8" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="10" max="10" width="67.14" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="11" max="11" width="11.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="12" max="12" width="16.29" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -19068,10 +19071,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -19079,23 +19082,23 @@
 </file>
 
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:L199"/>
   <sheetFormatPr defaultColWidth="8.6875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="8.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="67.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="11.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="16.29"/>
+    <col min="1" max="1" width="11.71" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="11.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="8.14" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="4" max="4" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="11.71" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="16.29" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="8" max="8" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="10" max="10" width="67.14" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="11" max="11" width="11.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="12" max="12" width="16.29" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21543,10 +21546,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -21554,19 +21557,19 @@
 </file>
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G11"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="19.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="20.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="19.3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="20.42"/>
+    <col min="1" max="1" width="11.71" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="19.3" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="20.42" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="5" max="5" width="11.71" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="19.3" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="20.42" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -21772,10 +21775,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -21783,31 +21786,31 @@
 </file>
 
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:W14"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="22.86"/>
+    <col min="1" max="1" width="17" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="5" max="5" width="17" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="9" max="9" width="17" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="10" max="10" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="11" max="11" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="13" max="13" width="17" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="14" max="14" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="15" max="15" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="17" max="17" width="17" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="18" max="18" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="19" max="19" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="21" max="21" width="17" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="22" max="22" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="23" max="23" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -22541,10 +22544,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -22552,31 +22555,31 @@
 </file>
 
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:W14"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="10.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="10.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="10.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="10.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="22.86"/>
+    <col min="1" max="1" width="10.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="5" max="5" width="10.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="9" max="9" width="10.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="10" max="10" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="11" max="11" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="13" max="13" width="10.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="14" max="14" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="15" max="15" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="17" max="17" width="10.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="18" max="18" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="19" max="19" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="21" max="21" width="10.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="22" max="22" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="23" max="23" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23310,10 +23313,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -23321,17 +23324,17 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:D13"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="6.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22.86"/>
+    <col min="1" max="1" width="11.71" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="11.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="6.71" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="4" max="4" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -23508,10 +23511,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -23519,31 +23522,31 @@
 </file>
 
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:W14"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="14.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="14.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="22.86"/>
+    <col min="1" max="1" width="14.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="5" max="5" width="14.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="9" max="9" width="14.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="10" max="10" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="11" max="11" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="13" max="13" width="14.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="14" max="14" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="15" max="15" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="17" max="17" width="14.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="18" max="18" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="19" max="19" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="21" max="21" width="14.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="22" max="22" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="23" max="23" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24277,10 +24280,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -24288,31 +24291,31 @@
 </file>
 
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:W10"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="14.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="14.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="17" min="17" style="0" width="14.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="18" min="18" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="19" min="19" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="21" style="0" width="14.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="22" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="22.86"/>
+    <col min="1" max="1" width="14.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="5" max="5" width="14.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="9" max="9" width="14.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="10" max="10" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="11" max="11" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="13" max="13" width="14.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="14" max="14" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="15" max="15" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="17" max="17" width="14.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="18" max="18" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="19" max="19" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="21" max="21" width="14.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="22" max="22" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="23" max="23" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -24822,10 +24825,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -24833,19 +24836,19 @@
 </file>
 
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="17"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22.86"/>
+    <col min="1" max="1" width="17" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="5" max="5" width="17" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25111,10 +25114,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -25122,19 +25125,19 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="10.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22.86"/>
+    <col min="1" max="1" width="10.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="5" max="5" width="10.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25400,10 +25403,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -25411,19 +25414,19 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22.86"/>
+    <col min="1" max="1" width="14.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="5" max="5" width="14.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25689,10 +25692,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -25700,19 +25703,19 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:G10"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="14.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="20.57"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="22.86"/>
+    <col min="1" max="1" width="14.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="5" max="5" width="14.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="20.57" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25898,10 +25901,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -25909,16 +25912,16 @@
 </file>
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.29"/>
+    <col min="1" max="1" width="7" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="12" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="16.28515625" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -25996,6 +25999,7 @@
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0"/>
       <c r="B8" s="0" t="s">
         <v>32</v>
       </c>
@@ -26010,8 +26014,8 @@
       <c r="B9" s="0" t="s">
         <v>1563</v>
       </c>
-      <c r="C9" s="0" t="n">
-        <v>0.015290488688668</v>
+      <c r="C9" s="0">
+        <v>0.015290488688667961</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26021,15 +26025,15 @@
       <c r="B10" s="0" t="s">
         <v>1564</v>
       </c>
-      <c r="C10" s="0" t="n">
-        <v>0.0668170628141222</v>
+      <c r="C10" s="0">
+        <v>0.066817062814122169</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -26037,14 +26041,14 @@
 </file>
 
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C10"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="1" style="0" width="11.71"/>
+    <col min="1" max="3" width="11.71" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -26155,10 +26159,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -26166,16 +26170,16 @@
 </file>
 
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C199"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="67.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.29"/>
+    <col min="1" max="1" width="67.14" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="11.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="16.29" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -28365,10 +28369,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -28376,16 +28380,16 @@
 </file>
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C199"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="67.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.41"/>
+    <col min="1" max="1" width="67.14" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="11.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="16.41" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30575,10 +30579,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -30586,20 +30590,20 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H13"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="3.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22.86"/>
+    <col min="1" max="1" width="11.71" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="11.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="3.14" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="4" max="4" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="11.71" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="16.29" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="8" max="8" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -30887,10 +30891,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -30898,16 +30902,16 @@
 </file>
 
 <file path=xl/worksheets/sheet30.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C199"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="67.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.41"/>
+    <col min="1" max="1" width="67.14" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="11.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="16.41" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -33061,10 +33065,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -33072,16 +33076,16 @@
 </file>
 
 <file path=xl/worksheets/sheet31.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C199"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="67.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.41"/>
+    <col min="1" max="1" width="67.14" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="11.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="16.41" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -35235,10 +35239,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -35246,22 +35250,22 @@
 </file>
 
 <file path=xl/worksheets/sheet32.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N29"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="30.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="30.28"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="13.43"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="22.86"/>
+    <col min="1" max="1" width="30.28" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="12.42" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="4" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="30.28" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="12.42" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="8" max="9" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="11" max="11" width="30.28" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="12" max="12" width="13.43" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="13" max="14" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -36149,10 +36153,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -36160,22 +36164,22 @@
 </file>
 
 <file path=xl/worksheets/sheet33.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N29"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="18.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="18.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="22.86"/>
+    <col min="1" max="1" width="18.29" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="12.71" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="4" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="18.29" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="12.42" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="8" max="9" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="11" max="11" width="18.29" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="12" max="12" width="12.42" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="13" max="14" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37063,10 +37067,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -37074,22 +37078,22 @@
 </file>
 
 <file path=xl/worksheets/sheet34.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N29"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="25.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="25.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="13.7"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="25.41"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="22.86"/>
+    <col min="1" max="1" width="25.41" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="12.71" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="4" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="25.41" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="13.7" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="8" max="9" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="11" max="11" width="25.41" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="12" max="12" width="12.42" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="13" max="14" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -37977,10 +37981,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -37988,22 +37992,22 @@
 </file>
 
 <file path=xl/worksheets/sheet35.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:N17"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="12.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="26"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12.42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="13" style="0" width="22.86"/>
+    <col min="1" max="1" width="26" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="12.42" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="4" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="26" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="12.42" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="8" max="9" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="11" max="11" width="26" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="12" max="12" width="12.42" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="13" max="14" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38507,10 +38511,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -38518,20 +38522,20 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H13"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="3.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22.86"/>
+    <col min="1" max="1" width="11.71" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="11.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="3.14" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="4" max="4" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="11.71" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="16.29" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="8" max="8" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38819,10 +38823,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -38830,20 +38834,20 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H13"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="3.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22.86"/>
+    <col min="1" max="1" width="11.71" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="11.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="3.14" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="4" max="4" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="11.71" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="16.29" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="8" max="8" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39131,10 +39135,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -39142,20 +39146,20 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H13"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="3.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22.86"/>
+    <col min="1" max="1" width="11.71" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="11.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="3.14" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="4" max="4" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="11.71" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="16.29" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="8" max="8" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39443,10 +39447,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -39454,20 +39458,20 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H13"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="3.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22.86"/>
+    <col min="1" max="1" width="11.71" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="11.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="3.14" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="4" max="4" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="11.71" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="16.29" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="8" max="8" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -39755,10 +39759,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -39766,20 +39770,20 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:H13"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="3.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="22.86"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="11.71"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="16.29"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="22.86"/>
+    <col min="1" max="1" width="11.71" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="11.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="3.14" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="4" max="4" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="6" max="6" width="11.71" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="7" max="7" width="16.29" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="8" max="8" width="22.86" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -40067,10 +40071,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
@@ -40078,16 +40082,16 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:C199"/>
   <sheetFormatPr defaultColWidth="8.6953125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="67.14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="11.99"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="16.29"/>
+    <col min="1" max="1" width="67.14" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="2" max="2" width="11.99" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
+    <col min="3" max="3" width="16.29" style="0" hidden="false" customWidth="true" outlineLevel="0" collapsed="false"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -42277,10 +42281,10 @@
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.747916666666667" right="0.747916666666667" top="0.984027777777778" bottom="0.984027777777778" header="0.511805555555555" footer="0.511805555555555"/>
+  <printOptions horizontalCentered="false" verticalCentered="false" headings="false" gridLines="false" gridLinesSet="true"/>
+  <pageMargins left="0.74791666666667" right="0.74791666666667" top="0.98402777777778" bottom="0.98402777777778" header="0.51180555555555" footer="0.51180555555555"/>
   <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
+  <headerFooter differentOddEven="false" differentFirst="false">
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
